--- a/r5-core-STU2-release-preparation/all-profiles.xlsx
+++ b/r5-core-STU2-release-preparation/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T12:45:21+00:00</t>
+    <t>2025-01-24T12:53:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-STU2-release-preparation/all-profiles.xlsx
+++ b/r5-core-STU2-release-preparation/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T12:53:09+00:00</t>
+    <t>2025-01-24T13:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
